--- a/E/MKTN.xlsx
+++ b/E/MKTN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5188" uniqueCount="2477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5198" uniqueCount="2481">
   <si>
     <t/>
   </si>
@@ -7438,10 +7438,22 @@
     <t>20143604</t>
   </si>
   <si>
-    <t>THRE PKT PLY 90G30H</t>
+    <t>THRE PKT PLY 9GB30H</t>
   </si>
   <si>
     <t>1061</t>
+  </si>
+  <si>
+    <t>20143598</t>
+  </si>
+  <si>
+    <t>1099</t>
+  </si>
+  <si>
+    <t>20143608</t>
+  </si>
+  <si>
+    <t>1100</t>
   </si>
 </sst>
 </file>
@@ -7834,7 +7846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F896"/>
+  <dimension ref="A1:F898"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -25201,6 +25213,40 @@
         <v>2476</v>
       </c>
     </row>
+    <row r="897" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A897" s="1" t="s">
+        <v>2477</v>
+      </c>
+      <c r="B897" s="1" t="s">
+        <v>2461</v>
+      </c>
+      <c r="C897" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D897" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E897" s="1" t="s">
+        <v>2478</v>
+      </c>
+    </row>
+    <row r="898" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A898" s="1" t="s">
+        <v>2479</v>
+      </c>
+      <c r="B898" s="1" t="s">
+        <v>2469</v>
+      </c>
+      <c r="C898" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D898" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E898" s="1" t="s">
+        <v>2480</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
